--- a/data/trans_bre/P1805_2016_2023-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1805_2016_2023-Edad-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 2,3</t>
+          <t>-1,92; 2,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 6,19</t>
+          <t>-3,97; 5,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 233,79</t>
+          <t>-69,11; 223,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-57,54; 318,41</t>
+          <t>-59,79; 292,74</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>1,23</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>45,59%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,42</t>
+          <t>-0,78; 2,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,87</t>
+          <t>-1,7; 3,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 455,39</t>
+          <t>-44,28; 352,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 320,44</t>
+          <t>-48,42; 242,25</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,36</t>
+          <t>-1,19; 2,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,51</t>
+          <t>-1,77; 2,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-37,74; 137,61</t>
+          <t>-37,97; 132,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-42,26; 86,82</t>
+          <t>-36,06; 102,09</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>-13,15%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,27</t>
+          <t>0,43; 4,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 3,21</t>
+          <t>-2,88; 1,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 333,21</t>
+          <t>9,11; 348,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 159,36</t>
+          <t>-44,46; 29,6</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>73,42%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,27</t>
+          <t>1,34; 6,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,14</t>
+          <t>0,23; 3,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,3; 689,27</t>
+          <t>34,98; 670,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 206,27</t>
+          <t>1,94; 190,28</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130,36%</t>
+          <t>274,38%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 6,05</t>
+          <t>1,0; 6,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,99</t>
+          <t>1,11; 3,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,94; 1626,31</t>
+          <t>37,26; 1576,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,27; 548,94</t>
+          <t>65,0; 908,54</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131,33%</t>
+          <t>131,77%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,57</t>
+          <t>0,59; 6,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,82</t>
+          <t>-0,09; 2,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 1359,38</t>
+          <t>-6,13; 1035,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 614,71</t>
+          <t>-15,75; 659,58</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,8</t>
+          <t>1,17; 2,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,86</t>
+          <t>-0,15; 1,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49,87; 189,32</t>
+          <t>54,0; 184,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 74,69</t>
+          <t>-4,4; 65,6</t>
         </is>
       </c>
     </row>
